--- a/docs/evidence/20261023_持有成本口徑差_B段/20261023_持有成本口徑差_B段.xlsx
+++ b/docs/evidence/20261023_持有成本口徑差_B段/20261023_持有成本口徑差_B段.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1201" uniqueCount="876">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="879">
   <si>
     <r>
       <rPr>
@@ -15740,6 +15740,74 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">決定（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Andy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：維持「不可分離」。補記：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OpenAI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">揭露支出分項，或揭露對 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Azure </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的實付價，才能分開。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
@@ -15910,6 +15978,74 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">決定（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Andy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：要；只寫進查證檔，不改模型（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tokenomics </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">維持 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
@@ -16111,6 +16247,150 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">節</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">決定（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Andy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">兩種配置並列即可，不再追；影響 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GB300 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">持有成本 −</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.38 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">至 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+0.33</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">±3%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），不改結論。</t>
     </r>
   </si>
   <si>
@@ -30820,45 +31100,54 @@
       <c r="F10" s="27" t="s">
         <v>695</v>
       </c>
+      <c r="G10" s="33" t="s">
+        <v>696</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>700</v>
+        <v>701</v>
+      </c>
+      <c r="G11" s="33" t="s">
+        <v>702</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="F12" s="27" t="s">
-        <v>705</v>
+        <v>707</v>
+      </c>
+      <c r="G12" s="33" t="s">
+        <v>708</v>
       </c>
     </row>
   </sheetData>
@@ -30892,17 +31181,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="35" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="36" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="37" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="B5" s="38"/>
       <c r="C5" s="38"/>
@@ -30915,42 +31204,42 @@
     </row>
     <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="39" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="C6" s="39" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="F6" s="39" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="G6" s="39" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="H6" s="39" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="I6" s="39" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="J6" s="39" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="K6" s="39" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="B7" s="28" t="n">
         <v>300</v>
@@ -30985,12 +31274,12 @@
         <v>1.28299453002706</v>
       </c>
       <c r="K7" s="27" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="B8" s="28" t="n">
         <v>300</v>
@@ -31002,7 +31291,7 @@
         <v>5</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="F8" s="29" t="n">
         <f aca="false">B8/C8</f>
@@ -31030,7 +31319,7 @@
     </row>
     <row r="9" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="B9" s="28" t="n">
         <v>300</v>
@@ -31065,12 +31354,12 @@
         <v>1.42554947780784</v>
       </c>
       <c r="K9" s="27" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="B10" s="28" t="n">
         <v>300</v>
@@ -31082,7 +31371,7 @@
         <v>4.5</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="F10" s="29" t="n">
         <f aca="false">B10/C10</f>
@@ -31110,12 +31399,12 @@
     </row>
     <row r="11" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="40" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="37" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="B13" s="38"/>
       <c r="C13" s="38"/>
@@ -31131,19 +31420,19 @@
         <v>2</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="C14" s="39" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="39" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="33" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="B15" s="28" t="n">
         <v>16</v>
@@ -31153,33 +31442,33 @@
       </c>
       <c r="D15" s="27"/>
       <c r="E15" s="27" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="33" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="B16" s="28" t="n">
         <v>0.6</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="D16" s="27"/>
       <c r="E16" s="33" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="33" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="B17" s="28" t="n">
         <v>1.9</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="D17" s="27"/>
       <c r="E17" s="33" t="s">
@@ -31188,39 +31477,39 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="33" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="B18" s="29" t="n">
         <f aca="false">(B16+B17)/2</f>
         <v>1.25</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="D18" s="27"/>
       <c r="E18" s="27" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="33" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="B19" s="41" t="n">
         <f aca="false">(B17-B16)/LN(B17/B16)</f>
         <v>1.12780698259266</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="27" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="33" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="B20" s="29" t="n">
         <f aca="false">B15/B18</f>
@@ -31231,12 +31520,12 @@
       </c>
       <c r="D20" s="27"/>
       <c r="E20" s="27" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="33" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="B21" s="29" t="n">
         <f aca="false">B15/B19</f>
@@ -31247,12 +31536,12 @@
       </c>
       <c r="D21" s="27"/>
       <c r="E21" s="27" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="33" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="B22" s="29" t="n">
         <f aca="false">B20/'TK 拆解'!G66</f>
@@ -31264,47 +31553,47 @@
       </c>
       <c r="D22" s="27"/>
       <c r="E22" s="27" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="42" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="39" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="B24" s="39" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="C24" s="39" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="D24" s="39" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="E24" s="39" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="F24" s="39" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="33" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="C25" s="29" t="n">
         <f aca="false">0.93*'TK 拆解'!G66*B18</f>
         <v>10.8730003702399</v>
       </c>
       <c r="D25" s="33" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="E25" s="27" t="s">
         <v>16</v>
@@ -31312,7 +31601,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="33" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="C26" s="29" t="n">
         <f aca="false">B15-C25</f>
@@ -31328,7 +31617,7 @@
     </row>
     <row r="27" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="33" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="C27" s="29" t="n">
         <f aca="false">0.93*'TK 拆解'!G66*B19</f>
@@ -31339,145 +31628,145 @@
         <v>0.386867713035539</v>
       </c>
       <c r="E27" s="27" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="27" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="F28" s="27" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="B29" s="33" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="C29" s="27" t="n">
         <f aca="false">B20*1000000000/('TK 拆解'!G35*8760)</f>
         <v>2.3137037549908</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="E29" s="27" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="27" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="27" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="B30" s="33" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="D30" s="27" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="E30" s="27" t="s">
         <v>24</v>
       </c>
       <c r="F30" s="27" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="27" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="D31" s="29" t="n">
         <f aca="false">B15/(B18/'TK 拆解'!C9)</f>
         <v>15.36</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="F31" s="27" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="27" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="C32" s="33" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D32" s="27" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="E32" s="33" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="F32" s="27" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="27" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="B33" s="33" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D33" s="33" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="E33" s="27" t="s">
         <v>24</v>
       </c>
       <c r="F33" s="33" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="33" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="B34" s="27"/>
       <c r="D34" s="27" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="E34" s="27"/>
       <c r="F34" s="27"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="37" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="B36" s="38"/>
       <c r="C36" s="38"/>
@@ -31493,7 +31782,7 @@
         <v>2</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="C37" s="39" t="s">
         <v>3</v>
@@ -31502,7 +31791,7 @@
         <v>198</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="F37" s="39" t="s">
         <v>11</v>
@@ -31510,7 +31799,7 @@
     </row>
     <row r="38" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="27" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B38" s="28" t="n">
         <v>5.8</v>
@@ -31519,33 +31808,33 @@
         <v>104</v>
       </c>
       <c r="F38" s="33" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="33" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="B39" s="28" t="n">
         <v>0.2</v>
       </c>
       <c r="C39" s="27" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="F39" s="33" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="27" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="B40" s="29" t="n">
         <f aca="false">B38/B39</f>
         <v>29</v>
       </c>
       <c r="C40" s="27" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="D40" s="29" t="n">
         <f aca="false">'TK 拆解'!E39</f>
@@ -31556,12 +31845,12 @@
         <v>0.899581179818709</v>
       </c>
       <c r="F40" s="27" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="33" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="B41" s="44" t="n">
         <v>9</v>
@@ -31578,12 +31867,12 @@
         <v>0.710339384372534</v>
       </c>
       <c r="F41" s="27" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="33" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="B42" s="44" t="n">
         <v>11</v>
@@ -31603,7 +31892,7 @@
     </row>
     <row r="43" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="27" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B43" s="28" t="n">
         <v>3</v>
@@ -31612,12 +31901,12 @@
         <v>75</v>
       </c>
       <c r="F43" s="33" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="27" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="B44" s="28" t="n">
         <v>2</v>
@@ -31626,12 +31915,12 @@
         <v>75</v>
       </c>
       <c r="F44" s="33" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="33" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="B45" s="45" t="n">
         <f aca="false">B41+B43+B44</f>
@@ -31645,43 +31934,43 @@
         <v>16</v>
       </c>
       <c r="F45" s="33" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="46" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="39" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="G47" s="39" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="H47" s="39" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="27" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="B48" s="29" t="n">
         <f aca="false">B40+B43</f>
@@ -31713,7 +32002,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="27" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="B49" s="29" t="n">
         <f aca="false">B40</f>
@@ -31745,7 +32034,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="27" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="B50" s="29" t="n">
         <f aca="false">B40</f>
@@ -31777,12 +32066,12 @@
     </row>
     <row r="51" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="40" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="122.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="33" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="B52" s="41" t="n">
         <f aca="false">0.15*9.7</f>
@@ -31800,12 +32089,12 @@
         <v>0.733871911435009</v>
       </c>
       <c r="F52" s="27" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="37" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="B54" s="38"/>
       <c r="C54" s="38"/>
@@ -31818,27 +32107,27 @@
     </row>
     <row r="55" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="39" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="D55" s="39" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="E55" s="39" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="F55" s="39" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="27" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="B56" s="48" t="n">
         <f aca="false">'TK 拆解'!C35</f>
@@ -31849,7 +32138,7 @@
         <v>1.54259654785589</v>
       </c>
       <c r="D56" s="29" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="E56" s="29" t="n">
         <f aca="false">D56/C56</f>
@@ -31861,7 +32150,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="27" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="B57" s="48" t="n">
         <f aca="false">'TK 拆解'!C35</f>
@@ -31872,7 +32161,7 @@
         <v>1.54259654785589</v>
       </c>
       <c r="D57" s="29" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="E57" s="29" t="n">
         <f aca="false">D57/C57</f>
@@ -31884,7 +32173,7 @@
     </row>
     <row r="58" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="33" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="B58" s="48" t="n">
         <f aca="false">'TK 拆解'!G35</f>
@@ -31903,12 +32192,12 @@
         <v>1.36852749869553</v>
       </c>
       <c r="F58" s="27" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="27" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="B59" s="48" t="n">
         <f aca="false">'TK 拆解'!E35</f>
@@ -31927,12 +32216,12 @@
         <v>0.891019087752603</v>
       </c>
       <c r="F59" s="27" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="27" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="B60" s="48" t="n">
         <f aca="false">'TK 拆解'!E35</f>
@@ -31956,7 +32245,7 @@
     </row>
     <row r="61" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="27" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="B61" s="48" t="n">
         <f aca="false">'TK 拆解'!F35</f>
@@ -31980,12 +32269,12 @@
     </row>
     <row r="62" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="40" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="37" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="B64" s="38"/>
       <c r="C64" s="38"/>
@@ -32001,10 +32290,10 @@
         <v>2</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="D65" s="39" t="s">
         <v>11</v>
@@ -32012,7 +32301,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="33" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="B66" s="28" t="n">
         <v>2575</v>
@@ -32021,12 +32310,12 @@
         <v>582.3</v>
       </c>
       <c r="D66" s="27" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="33" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="B67" s="28" t="n">
         <v>879</v>
@@ -32038,18 +32327,18 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="33" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="B68" s="28" t="n">
         <v>1507</v>
       </c>
       <c r="D68" s="27" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="33" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="B69" s="28" t="n">
         <v>1400</v>
@@ -32058,12 +32347,12 @@
         <v>259.7</v>
       </c>
       <c r="D69" s="27" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="33" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="B70" s="43" t="n">
         <f aca="false">B67/B66</f>
@@ -32077,7 +32366,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="33" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="B71" s="43" t="n">
         <f aca="false">B69/B66</f>
@@ -32091,19 +32380,19 @@
     </row>
     <row r="72" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="33" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="B72" s="45" t="n">
         <f aca="false">B66-B67-B68</f>
         <v>189</v>
       </c>
       <c r="D72" s="33" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="27" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="B73" s="49" t="n">
         <f aca="false">B72/B66</f>
@@ -32113,31 +32402,31 @@
     </row>
     <row r="74" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="27" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="B74" s="43" t="n">
         <f aca="false">('TK 拆解'!G54+'TK 拆解'!G60+'TK 拆解'!G62+'TK 拆解'!G63+0.005*'TK 拆解'!G46)/'TK 拆解'!G66</f>
         <v>0.301117708134952</v>
       </c>
       <c r="D74" s="27" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="27" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="B75" s="43" t="n">
         <f aca="false">'TK 拆解'!G39/'TK 拆解'!E11/'TK 拆解'!G66</f>
         <v>0.465302877791437</v>
       </c>
       <c r="D75" s="27" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="27" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B76" s="50" t="n">
         <f aca="false">1</f>
@@ -32148,12 +32437,12 @@
         <v>1.5</v>
       </c>
       <c r="D76" s="27" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="33" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="B77" s="29" t="n">
         <f aca="false">(B76+C76)/2</f>
@@ -32163,19 +32452,19 @@
     </row>
     <row r="78" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="33" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B78" s="29" t="n">
         <f aca="false">B66*4/1000/B77</f>
         <v>8.24</v>
       </c>
       <c r="D78" s="27" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="27" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="B79" s="29" t="n">
         <f aca="false">B78/'TK 拆解'!G66</f>
@@ -32185,38 +32474,38 @@
     </row>
     <row r="80" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="33" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="B80" s="29" t="n">
         <f aca="false">B78*1000000000/('TK 拆解'!G35*8760)</f>
         <v>1.48944679227533</v>
       </c>
       <c r="D80" s="33" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="27" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="B81" s="27" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C81" s="27"/>
       <c r="D81" s="33" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="33" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="B82" s="27" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="C82" s="27"/>
       <c r="D82" s="33" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
     </row>
   </sheetData>

--- a/docs/evidence/20261023_持有成本口徑差_B段/20261023_持有成本口徑差_B段.xlsx
+++ b/docs/evidence/20261023_持有成本口徑差_B段/20261023_持有成本口徑差_B段.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1391" uniqueCount="989">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="991">
   <si>
     <r>
       <rPr>
@@ -7315,7 +7315,7 @@
     <t xml:space="preserve">隱含 WACC（使 TK GB300 持有成本＝IREN 租金 9.70；Derived）：</t>
   </si>
   <si>
-    <t xml:space="preserve">依序：IT 6 年＋TK 營運費；IT 5 年＋TK 營運費；IT 6 年＋IREN 隱含營運費；IT 5 年＋IREN 隱含營運費</t>
+    <t xml:space="preserve">已被 B 段第6節取代：此值是固定 TK 的 capex 與營運下求得，混入了 capex 與營運差異。以 IREN 自己的 capex 反推：營運取下界 1.455 時 9.0–10.2%（上限），取 TK 營運 1.98 時 7.2–8.4%。</t>
   </si>
   <si>
     <r>
@@ -16836,7 +16836,45 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">決定：不改模型；同列 </t>
+      <t xml:space="preserve">決定（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Andy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-23</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：不改模型；同列 </t>
     </r>
     <r>
       <rPr>
@@ -16855,7 +16893,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">與出租方 </t>
+      <t xml:space="preserve">與出租方折現率。「</t>
     </r>
     <r>
       <rPr>
@@ -16867,6 +16905,91 @@
       </rPr>
       <t xml:space="preserve">3–8%</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」已被 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">取代，改依公司分列（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IREN 3.31%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CoreWeave </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">債務 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9.6–9.9%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
   </si>
   <si>
     <r>
@@ -18250,17 +18373,1360 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">是（待 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">inbox</t>
+      <t xml:space="preserve">要，只寫進查證檔不改模型；債務利率已取得（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">段第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">節），</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">active power </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">定義與 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">耐用年限待 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10-Q </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">後半</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">維持 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3–8% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">區間</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">把 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">WACC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">差異從假設變成實值</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">段頁第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">節</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">決定（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Andy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：要，只寫查證檔不改模型。狀態：部分完成（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10-Q </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">只讀前約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">80/181 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頁；債務利率已取得）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IREN </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">叢集部署 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 $M/MW </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">是否已在 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.8B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">內？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">原文未明，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A/B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">兩配置並列</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">向 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IREN </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">簡報原頁確認</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不影響總 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">capex</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；影響 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／廠房側拆分</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">段頁第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">節</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">決定（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Andy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">兩種配置並列即可，不再追；影響 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GB300 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">持有成本 −</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.38 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">至 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+0.33</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">±3%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），不改結論。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">是否把 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Project </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">決定第 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">題的「出租方折現率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3–8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」改為依公司分列？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">是：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IREN 3.31%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（個案）、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CoreWeave </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">債務 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9.6–9.9%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">README </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已據此撤回「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">WACC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">是主因」</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">WACC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">主因」結論被推翻：以 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IREN </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">自己的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">capex </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">與營運反推，隱含 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">WACC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9–10%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；差額主因為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">設備單價與營運費用</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">段頁第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">節；證據 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">E26</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">決定（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Andy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-23</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：改為依公司分列。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IREN 3.31% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">是 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Microsoft </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">擔保加預付款的個案，不能代表出租方</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TK GB300 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">設備（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">32.2 $B/GW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）比 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IREN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">29.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）高 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，且營運費用高 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">36%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：要查嗎？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">先不改模型；列為待查（機架單價 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4.3M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">密度 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">kW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GPU</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Dell </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">大單折扣、營運範圍定義）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TK </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">下調</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">兩項合計約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.27 $B/GW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12%</t>
     </r>
     <r>
       <rPr>
@@ -18277,66 +19743,6 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">維持 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3–8% </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">區間</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">把 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">WACC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">差異從假設變成實值</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
@@ -18360,7 +19766,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">5</t>
+      <t xml:space="preserve">6</t>
     </r>
     <r>
       <rPr>
@@ -18399,48 +19805,27 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）：要；只寫進查證檔，不改模型（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Tokenomics </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">維持 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）。</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">）：先不改模型，列為證據待查。兩項合計約占持有成本 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，目前只有 </t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -18458,1038 +19843,26 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">叢集部署 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3 $M/MW </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">是否已在 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5.8B </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">內？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">原文未明，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A/B </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">兩配置並列</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">向 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">IREN </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">簡報原頁確認</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">不影響總 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">capex</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；影響 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">IT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／廠房側拆分</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">段頁第</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">節</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">決定（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Andy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">兩種配置並列即可，不再追；影響 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GB300 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">持有成本 −</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.38 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">至 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+0.33</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（約 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">±3%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">），不改結論。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">是否把 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Project </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">決定第 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">題的「出租方折現率 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3–8%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">」改為依公司分列？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">是：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">IREN 3.31%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（個案）、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CoreWeave </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">債務 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9.6–9.9%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">README </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已據此撤回「</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">WACC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">是主因」</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">「</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">WACC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">主因」結論被推翻：以 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">IREN </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">自己的 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">capex </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">與營運反推，隱含 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">WACC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">約 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9–10%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；差額主因為 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">IT </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">設備單價與營運費用</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">段頁第</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">節；證據 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">E26</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">TK GB300 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">的 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">IT </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">設備（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">32.2 $B/GW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）比 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">IREN</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">29.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）高 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">11%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，且營運費用高 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">36%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：要查嗎？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">先不改模型；列為待查（機架單價 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4.3M</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GPU </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">密度 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">kW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GPU</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Dell </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">大單折扣、營運範圍定義）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">TK </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">下調</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">兩項合計約 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.27 $B/GW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（約 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">段頁第</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">節</t>
+      <t xml:space="preserve">一個對照點，營運 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.455 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">只是下界（不含企業管理費）；等有第二個對照點再判斷</t>
     </r>
   </si>
   <si>
@@ -27940,26 +28313,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">未取得（待 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Drive inbox </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">的 </t>
+      <t xml:space="preserve">部分取得（</t>
     </r>
     <r>
       <rPr>
@@ -27978,10 +28332,57 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">全文）</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">只讀前約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">80/181 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頁）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">債務利率已取得（第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">節）；</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -28018,56 +28419,56 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">耐用年限、債務利率</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">→ 有了債務利率才能把「出租方折現率 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3–8%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">」落到 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CoreWeave </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">實值</t>
+      <t xml:space="preserve">耐用年限仍未取得</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">→ 債務利率已用於第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">節：出租方折現率改依公司分列（待判斷 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，已決定）</t>
     </r>
   </si>
   <si>
@@ -39162,7 +39563,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="n">
         <v>10</v>
       </c>
@@ -39227,25 +39628,31 @@
       <c r="F13" s="27" t="s">
         <v>730</v>
       </c>
+      <c r="G13" s="32" t="s">
+        <v>731</v>
+      </c>
     </row>
-    <row r="14" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="27" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F14" s="27" t="s">
-        <v>735</v>
+        <v>736</v>
+      </c>
+      <c r="G14" s="32" t="s">
+        <v>737</v>
       </c>
     </row>
   </sheetData>
@@ -39279,17 +39686,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="36" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="37" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="38" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B5" s="39"/>
       <c r="C5" s="39"/>
@@ -39302,42 +39709,42 @@
     </row>
     <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="40" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="C6" s="40" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="G6" s="40" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="H6" s="40" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="I6" s="40" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="J6" s="40" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="K6" s="40" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B7" s="28" t="n">
         <v>300</v>
@@ -39372,12 +39779,12 @@
         <v>1.28299453002706</v>
       </c>
       <c r="K7" s="27" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="B8" s="28" t="n">
         <v>300</v>
@@ -39389,7 +39796,7 @@
         <v>5</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="F8" s="29" t="n">
         <f aca="false">B8/C8</f>
@@ -39417,7 +39824,7 @@
     </row>
     <row r="9" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="B9" s="28" t="n">
         <v>300</v>
@@ -39452,12 +39859,12 @@
         <v>1.42554947780784</v>
       </c>
       <c r="K9" s="27" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="B10" s="28" t="n">
         <v>300</v>
@@ -39469,7 +39876,7 @@
         <v>4.5</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="F10" s="29" t="n">
         <f aca="false">B10/C10</f>
@@ -39497,12 +39904,12 @@
     </row>
     <row r="11" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="41" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="38" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="B13" s="39"/>
       <c r="C13" s="39"/>
@@ -39518,21 +39925,21 @@
         <v>2</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="D14" s="40" t="s">
         <v>3</v>
       </c>
       <c r="E14" s="40" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="32" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B15" s="28" t="n">
         <v>16.3</v>
@@ -39544,32 +39951,32 @@
         <v>104</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="32" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="B16" s="28" t="n">
         <v>0.6</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="32" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="B17" s="28" t="n">
         <v>1.9</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="E17" s="32" t="s">
         <v>440</v>
@@ -39577,37 +39984,37 @@
     </row>
     <row r="18" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="32" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="B18" s="29" t="n">
         <f aca="false">(B16+B17)/2</f>
         <v>1.25</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="32" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="B19" s="42" t="n">
         <f aca="false">(B17-B16)/LN(B17/B16)</f>
         <v>1.12780698259266</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="32" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B20" s="29" t="n">
         <f aca="false">B15/B18</f>
@@ -39621,12 +40028,12 @@
         <v>68</v>
       </c>
       <c r="E20" s="27" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="32" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B21" s="29" t="n">
         <f aca="false">B15/B19</f>
@@ -39640,12 +40047,12 @@
         <v>68</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="32" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="B22" s="29" t="n">
         <f aca="false">B20/'TK 拆解'!G66</f>
@@ -39659,12 +40066,12 @@
         <v>26</v>
       </c>
       <c r="E22" s="27" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="32" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B23" s="29" t="n">
         <f aca="false">B21/'TK 拆解'!G66</f>
@@ -39678,23 +40085,23 @@
         <v>26</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="43" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="40" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="D25" s="40" t="s">
         <v>3</v>
@@ -39705,7 +40112,7 @@
     </row>
     <row r="26" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="32" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B26" s="29" t="n">
         <f aca="false">0.93*'TK 拆解'!G66*B18</f>
@@ -39719,12 +40126,12 @@
         <v>104</v>
       </c>
       <c r="E26" s="32" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="32" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="B27" s="29" t="n">
         <f aca="false">B15-B26</f>
@@ -39738,12 +40145,12 @@
         <v>104</v>
       </c>
       <c r="E27" s="32" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="32" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="B28" s="44" t="n">
         <f aca="false">B27/B15</f>
@@ -39760,7 +40167,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="32" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="B29" s="29" t="n">
         <f aca="false">0.93*'TK 拆解'!G66*B19</f>
@@ -39777,7 +40184,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="32" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="B30" s="29" t="n">
         <f aca="false">B15-B29</f>
@@ -39791,12 +40198,12 @@
         <v>104</v>
       </c>
       <c r="E30" s="27" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="32" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="B31" s="44" t="n">
         <f aca="false">B30/B15</f>
@@ -39813,165 +40220,165 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="43" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="40" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="B33" s="40" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C33" s="40" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="D33" s="40" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="E33" s="40" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="F33" s="40" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="27" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="B34" s="32" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C34" s="32" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="D34" s="32" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="E34" s="32" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="F34" s="27" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="27" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="B35" s="32" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="C35" s="29" t="n">
         <f aca="false">B20*1000000000/('TK 拆解'!G35*8760)</f>
         <v>2.35708570039688</v>
       </c>
       <c r="D35" s="32" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="E35" s="27" t="s">
         <v>16</v>
       </c>
       <c r="F35" s="27" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="27" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B36" s="32" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="C36" s="32" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="D36" s="27" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="E36" s="27" t="s">
         <v>24</v>
       </c>
       <c r="F36" s="27" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="27" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="B37" s="32" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="C37" s="29" t="n">
         <f aca="false">B15/(B18/'TK 拆解'!C9)</f>
         <v>15.648</v>
       </c>
       <c r="D37" s="32" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="E37" s="27" t="s">
         <v>16</v>
       </c>
       <c r="F37" s="27" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="27" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B38" s="32" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="C38" s="32" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="D38" s="27" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="E38" s="32" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="F38" s="27" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="27" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B39" s="32" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C39" s="32" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="D39" s="32" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="E39" s="27" t="s">
         <v>24</v>
       </c>
       <c r="F39" s="32" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="32" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="B40" s="27"/>
       <c r="D40" s="27" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="E40" s="27"/>
       <c r="F40" s="27"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="38" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="B42" s="39"/>
       <c r="C42" s="39"/>
@@ -39987,7 +40394,7 @@
         <v>2</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C43" s="40" t="s">
         <v>3</v>
@@ -39996,7 +40403,7 @@
         <v>198</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="F43" s="40" t="s">
         <v>11</v>
@@ -40004,7 +40411,7 @@
     </row>
     <row r="44" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="27" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B44" s="28" t="n">
         <v>5.8</v>
@@ -40013,33 +40420,33 @@
         <v>104</v>
       </c>
       <c r="F44" s="32" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="32" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="B45" s="28" t="n">
         <v>0.2</v>
       </c>
       <c r="C45" s="27" t="s">
+        <v>837</v>
+      </c>
+      <c r="F45" s="32" t="s">
         <v>835</v>
-      </c>
-      <c r="F45" s="32" t="s">
-        <v>833</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="27" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B46" s="29" t="n">
         <f aca="false">B44/B45</f>
         <v>29</v>
       </c>
       <c r="C46" s="27" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="D46" s="29" t="n">
         <f aca="false">'TK 拆解'!E39</f>
@@ -40050,12 +40457,12 @@
         <v>0.899581179818709</v>
       </c>
       <c r="F46" s="27" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="32" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="B47" s="45" t="n">
         <v>9</v>
@@ -40072,12 +40479,12 @@
         <v>0.710339384372534</v>
       </c>
       <c r="F47" s="27" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="32" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="B48" s="45" t="n">
         <v>11</v>
@@ -40097,7 +40504,7 @@
     </row>
     <row r="49" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="27" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B49" s="28" t="n">
         <v>3</v>
@@ -40106,12 +40513,12 @@
         <v>75</v>
       </c>
       <c r="F49" s="32" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="27" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="B50" s="28" t="n">
         <v>2</v>
@@ -40120,12 +40527,12 @@
         <v>75</v>
       </c>
       <c r="F50" s="32" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="32" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B51" s="46" t="n">
         <f aca="false">B47+B49+B50</f>
@@ -40139,43 +40546,43 @@
         <v>16</v>
       </c>
       <c r="F51" s="32" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="47" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="40" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="G53" s="40" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="H53" s="40" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="27" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="B54" s="29" t="n">
         <f aca="false">B46+B49</f>
@@ -40207,7 +40614,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="27" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="B55" s="29" t="n">
         <f aca="false">B46</f>
@@ -40239,7 +40646,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="27" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="B56" s="29" t="n">
         <f aca="false">B46</f>
@@ -40271,12 +40678,12 @@
     </row>
     <row r="57" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="41" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="122.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="32" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="B58" s="42" t="n">
         <f aca="false">0.15*9.7</f>
@@ -40294,12 +40701,12 @@
         <v>0.733871911435009</v>
       </c>
       <c r="F58" s="27" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="38" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="B60" s="39"/>
       <c r="C60" s="39"/>
@@ -40312,27 +40719,27 @@
     </row>
     <row r="61" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="40" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="D61" s="40" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="E61" s="40" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="F61" s="40" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="27" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="B62" s="49" t="n">
         <f aca="false">'TK 拆解'!C35</f>
@@ -40343,7 +40750,7 @@
         <v>1.54259654785589</v>
       </c>
       <c r="D62" s="29" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="E62" s="29" t="n">
         <f aca="false">D62/C62</f>
@@ -40355,7 +40762,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="27" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B63" s="49" t="n">
         <f aca="false">'TK 拆解'!C35</f>
@@ -40366,7 +40773,7 @@
         <v>1.54259654785589</v>
       </c>
       <c r="D63" s="29" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E63" s="29" t="n">
         <f aca="false">D63/C63</f>
@@ -40378,7 +40785,7 @@
     </row>
     <row r="64" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="32" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="B64" s="49" t="n">
         <f aca="false">'TK 拆解'!G35</f>
@@ -40397,12 +40804,12 @@
         <v>1.39418738929607</v>
       </c>
       <c r="F64" s="27" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="27" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="B65" s="49" t="n">
         <f aca="false">'TK 拆解'!E35</f>
@@ -40421,12 +40828,12 @@
         <v>0.891019087752603</v>
       </c>
       <c r="F65" s="27" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="27" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="B66" s="49" t="n">
         <f aca="false">'TK 拆解'!E35</f>
@@ -40450,7 +40857,7 @@
     </row>
     <row r="67" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="27" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="B67" s="49" t="n">
         <f aca="false">'TK 拆解'!F35</f>
@@ -40474,12 +40881,12 @@
     </row>
     <row r="68" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="41" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="38" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="B70" s="39"/>
       <c r="C70" s="39"/>
@@ -40495,10 +40902,10 @@
         <v>2</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="D71" s="40" t="s">
         <v>11</v>
@@ -40506,7 +40913,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="32" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="B72" s="28" t="n">
         <v>2575</v>
@@ -40515,12 +40922,12 @@
         <v>582.3</v>
       </c>
       <c r="D72" s="27" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="32" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="B73" s="28" t="n">
         <v>879</v>
@@ -40532,18 +40939,18 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="32" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="B74" s="28" t="n">
         <v>1507</v>
       </c>
       <c r="D74" s="27" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="32" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="B75" s="28" t="n">
         <v>1400</v>
@@ -40552,12 +40959,12 @@
         <v>259.7</v>
       </c>
       <c r="D75" s="27" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="32" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="B76" s="44" t="n">
         <f aca="false">B73/B72</f>
@@ -40571,7 +40978,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="32" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="B77" s="44" t="n">
         <f aca="false">B75/B72</f>
@@ -40585,19 +40992,19 @@
     </row>
     <row r="78" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="32" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="B78" s="46" t="n">
         <f aca="false">B72-B73-B74</f>
         <v>189</v>
       </c>
       <c r="D78" s="32" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="27" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="B79" s="50" t="n">
         <f aca="false">B78/B72</f>
@@ -40607,53 +41014,53 @@
     </row>
     <row r="80" customFormat="false" ht="149.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="27" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="B80" s="44" t="n">
         <f aca="false">('TK 拆解'!G54+'TK 拆解'!G60+'TK 拆解'!G62+'TK 拆解'!G63+0.005*'TK 拆解'!G46)/'TK 拆解'!G66</f>
         <v>0.301117708134952</v>
       </c>
       <c r="D80" s="27" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="27" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="B81" s="44" t="n">
         <f aca="false">'TK 拆解'!G39/'TK 拆解'!E11/'TK 拆解'!G66</f>
         <v>0.465302877791437</v>
       </c>
       <c r="D81" s="27" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="27" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="B82" s="51" t="n">
         <v>1</v>
       </c>
       <c r="D82" s="32" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="27" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="B83" s="51" t="n">
         <v>1.5</v>
       </c>
       <c r="D83" s="27" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="32" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="B84" s="29" t="n">
         <f aca="false">(B82+B83)/2</f>
@@ -40663,19 +41070,19 @@
     </row>
     <row r="85" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="32" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="B85" s="29" t="n">
         <f aca="false">B72*4/1000/B84</f>
         <v>8.24</v>
       </c>
       <c r="D85" s="27" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="27" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="B86" s="29" t="n">
         <f aca="false">B85/'TK 拆解'!G66</f>
@@ -40685,43 +41092,43 @@
     </row>
     <row r="87" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="32" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="B87" s="29" t="n">
         <f aca="false">B85*1000000000/('TK 拆解'!G35*8760)</f>
         <v>1.48944679227533</v>
       </c>
       <c r="D87" s="32" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="27" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B88" s="27" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="C88" s="27"/>
       <c r="D88" s="32" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="32" t="s">
-        <v>913</v>
-      </c>
-      <c r="B89" s="27" t="s">
-        <v>914</v>
+        <v>915</v>
+      </c>
+      <c r="B89" s="32" t="s">
+        <v>916</v>
       </c>
       <c r="C89" s="27"/>
       <c r="D89" s="32" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="38" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="B91" s="39"/>
       <c r="C91" s="39"/>
@@ -40734,18 +41141,18 @@
     </row>
     <row r="92" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="41" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="5" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="B93" s="40" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="C93" s="40" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="D93" s="40" t="s">
         <v>470</v>
@@ -40756,7 +41163,7 @@
     </row>
     <row r="94" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="27" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="B94" s="52" t="n">
         <v>0.15</v>
@@ -40765,15 +41172,15 @@
         <v>1300</v>
       </c>
       <c r="D94" s="27" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="E94" s="27" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="27" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="B95" s="52" t="n">
         <v>0.11</v>
@@ -40782,15 +41189,15 @@
         <v>3190</v>
       </c>
       <c r="D95" s="27" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="E95" s="27" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="27" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="B96" s="52" t="n">
         <v>0.09</v>
@@ -40799,15 +41206,15 @@
         <v>3000</v>
       </c>
       <c r="D96" s="27" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="E96" s="27" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="27" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="B97" s="52" t="n">
         <v>0.09</v>
@@ -40816,15 +41223,15 @@
         <v>2215</v>
       </c>
       <c r="D97" s="27" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="E97" s="27" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="27" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B98" s="52" t="n">
         <v>0.09</v>
@@ -40833,15 +41240,15 @@
         <v>1101</v>
       </c>
       <c r="D98" s="27" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="E98" s="27" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="27" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="B99" s="52" t="n">
         <v>0.07</v>
@@ -40850,15 +41257,15 @@
         <v>2837</v>
       </c>
       <c r="D99" s="27" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="E99" s="27" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="27" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="B100" s="52" t="n">
         <v>0.1</v>
@@ -40867,15 +41274,15 @@
         <v>2000</v>
       </c>
       <c r="D100" s="32" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="E100" s="27" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="27" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="B101" s="52" t="n">
         <v>0.1</v>
@@ -40884,15 +41291,15 @@
         <v>1750</v>
       </c>
       <c r="D101" s="32" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="E101" s="27" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="27" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="B102" s="52" t="n">
         <v>0.1</v>
@@ -40901,15 +41308,15 @@
         <v>2750</v>
       </c>
       <c r="D102" s="32" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="E102" s="27" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="27" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="B103" s="52" t="n">
         <v>0.1</v>
@@ -40918,15 +41325,15 @@
         <v>1250</v>
       </c>
       <c r="D103" s="32" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="E103" s="27" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="27" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="B104" s="52" t="n">
         <v>0.09</v>
@@ -40935,15 +41342,15 @@
         <v>2279</v>
       </c>
       <c r="D104" s="32" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="E104" s="27" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="27" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="B105" s="52" t="n">
         <v>0.02</v>
@@ -40952,15 +41359,15 @@
         <v>2588</v>
       </c>
       <c r="D105" s="32" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="E105" s="27" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="27" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="B106" s="52" t="n">
         <v>0.02</v>
@@ -40969,15 +41376,15 @@
         <v>4000</v>
       </c>
       <c r="D106" s="32" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="E106" s="27" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="27" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="B107" s="52" t="n">
         <v>0.11</v>
@@ -40986,15 +41393,15 @@
         <v>4220</v>
       </c>
       <c r="D107" s="32" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="E107" s="27" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="27" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="B108" s="52" t="n">
         <v>0.09</v>
@@ -41003,15 +41410,15 @@
         <v>882</v>
       </c>
       <c r="D108" s="32" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="E108" s="27" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="27" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="B109" s="52" t="n">
         <v>0.12</v>
@@ -41020,15 +41427,15 @@
         <v>189</v>
       </c>
       <c r="D109" s="32" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="E109" s="27" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="32" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="B110" s="50" t="n">
         <f aca="false">SUMPRODUCT(B94:B109,C94:C109)/SUM(C94:C109)</f>
@@ -41040,12 +41447,12 @@
       </c>
       <c r="D110" s="27"/>
       <c r="E110" s="27" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="32" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="B111" s="50" t="n">
         <f aca="false">SUMPRODUCT((D94:D109&lt;&gt;"可轉債")*B94:B109*C94:C109)/SUMPRODUCT((D94:D109&lt;&gt;"可轉債")*C94:C109)</f>
@@ -41058,7 +41465,7 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="32" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="B112" s="50" t="n">
         <f aca="false">SUMPRODUCT((D94:D109="DDTL")*B94:B109*C94:C109)/SUMPRODUCT((D94:D109="DDTL")*C94:C109)</f>
@@ -41071,7 +41478,7 @@
     </row>
     <row r="113" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="27" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="B113" s="50" t="n">
         <f aca="false">640*4/C110</f>
@@ -41079,24 +41486,24 @@
       </c>
       <c r="D113" s="27"/>
       <c r="E113" s="27" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="27" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="B114" s="54" t="n">
         <v>0.0331</v>
       </c>
       <c r="D114" s="27"/>
       <c r="E114" s="27" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="27" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="B115" s="50" t="n">
         <f aca="false">'TK 拆解'!E10</f>
@@ -41109,41 +41516,41 @@
     </row>
     <row r="116" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="41" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="5" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="E118" s="40" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="F118" s="40" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="G118" s="40" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="H118" s="40" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="I118" s="40" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="27" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="B119" s="48" t="n">
         <f aca="false">B46+B49</f>
@@ -41179,7 +41586,7 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="27" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="B120" s="48" t="n">
         <f aca="false">B46</f>
@@ -41215,7 +41622,7 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="27" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="B121" s="48" t="n">
         <f aca="false">B46</f>
@@ -41251,18 +41658,18 @@
     </row>
     <row r="122" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="41" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="40" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="B123" s="40" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="C123" s="40" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="D123" s="40" t="s">
         <v>11</v>
@@ -41270,7 +41677,7 @@
     </row>
     <row r="124" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="27" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="B124" s="50" t="n">
         <v>0.0902251768770876</v>
@@ -41279,12 +41686,12 @@
         <v>0.0718799483496657</v>
       </c>
       <c r="D124" s="32" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="27" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="B125" s="50" t="n">
         <v>0.101506699451234</v>
@@ -41293,12 +41700,12 @@
         <v>0.0837541071211492</v>
       </c>
       <c r="D125" s="32" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="27" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="B126" s="50" t="n">
         <v>0.093926343332646</v>
@@ -41307,20 +41714,20 @@
         <v>0.0768570214096538</v>
       </c>
       <c r="D126" s="32" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="41" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="5" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="B129" s="40" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="C129" s="5"/>
       <c r="D129" s="40" t="s">
@@ -41329,31 +41736,31 @@
     </row>
     <row r="130" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="32" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="B130" s="29" t="n">
         <f aca="false">B72*4/1000/B84</f>
         <v>8.24</v>
       </c>
       <c r="D130" s="32" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="32" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="B131" s="29" t="n">
         <f aca="false">B130*'TK 拆解'!C9</f>
         <v>9.888</v>
       </c>
       <c r="D131" s="32" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="27" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="B132" s="29" t="n">
         <f aca="false">B130/'TK 拆解'!G66</f>
@@ -41367,31 +41774,31 @@
     </row>
     <row r="133" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="32" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="B133" s="50" t="n">
         <f aca="false">0.05+(B130-'TK 拆解'!G80)/('TK 拆解'!G81-'TK 拆解'!G80)*0.03</f>
         <v>0.0583417039461151</v>
       </c>
       <c r="D133" s="32" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="32" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="B134" s="50" t="n">
         <f aca="false">0.1+(B131-'TK 拆解'!G82)/('TK 拆解'!G83-'TK 拆解'!G82)*0.03</f>
         <v>0.118748417688062</v>
       </c>
       <c r="D134" s="32" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="32" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="B135" s="46" t="n">
         <f aca="false">B72-B73-B74</f>
@@ -41403,7 +41810,7 @@
     </row>
     <row r="136" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="32" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="B136" s="46" t="n">
         <f aca="false">B135+49</f>
@@ -41414,24 +41821,24 @@
         <v>0.0924271844660194</v>
       </c>
       <c r="D136" s="27" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="32" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="B137" s="44" t="n">
         <f aca="false">640/B72</f>
         <v>0.248543689320388</v>
       </c>
       <c r="D137" s="32" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="122.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="41" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
     </row>
   </sheetData>
